--- a/data/trans_dic/IP22D6_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP22D6_R_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
